--- a/questions.xlsx
+++ b/questions.xlsx
@@ -1280,7 +1280,7 @@
   <dimension ref="A1:I61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" customWidth="1"/>
     <col min="2" max="2" width="42.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.5703125" customWidth="1"/>
     <col min="4" max="4" width="44.5703125" bestFit="1" customWidth="1"/>
